--- a/plate3d/PLATE3D_TEMPLATE.xlsx
+++ b/plate3d/PLATE3D_TEMPLATE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="237">
   <si>
     <t># PLATE3D  ·  blank input sheet</t>
   </si>
@@ -229,6 +229,54 @@
     <t>#   corner - the inner one is r minus the wall and is not asked for.</t>
   </si>
   <si>
+    <t>#   A TAPER makes ONE member that flows from one section into the other. Both</t>
+  </si>
+  <si>
+    <t>#   sections must be defined above, and both are read for their SHAPE ONLY -</t>
+  </si>
+  <si>
+    <t>#   their own length and base.pt are not used. The length is on this row.</t>
+  </si>
+  <si>
+    <t># TAPER</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>start.pt</t>
+  </si>
+  <si>
+    <t>end.pt</t>
+  </si>
+  <si>
+    <t>taper.pt</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>#   start.pt / end.pt say which named point of each section lands on the same</t>
+  </si>
+  <si>
+    <t>#   axis: bc bc keeps the underside flat, bc tc makes it eccentric. taper.pt is</t>
+  </si>
+  <si>
+    <t>#   the point a MODULE row grips, and it is measured on the START section.</t>
+  </si>
+  <si>
+    <t>#   The two must be the SAME SHAPE at different sizes - same family, same number</t>
+  </si>
+  <si>
+    <t>#   of corners, both solid or both hollow - or the row is refused by number.</t>
+  </si>
+  <si>
+    <t>#   A taper runs end to end. Part of a member cannot taper: split it in two.</t>
+  </si>
+  <si>
     <t># HOLE</t>
   </si>
   <si>
@@ -280,6 +328,36 @@
     <t>[repeat2]</t>
   </si>
   <si>
+    <t># NOTCH</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>#   A CUT that only runs over a STRETCH of the member, from - to along its own</t>
+  </si>
+  <si>
+    <t>#   axis. A NOTCH over the whole length is the same steel as a CUT.</t>
+  </si>
+  <si>
+    <t>#   L.X may name a place instead of a number - wt / wb are the web meeting a</t>
+  </si>
+  <si>
+    <t>#   flange, which a bounding box has not got. Then leave L.Y empty.</t>
+  </si>
+  <si>
+    <t>#   Not on a tapered member: what a cut takes out of a section that changes</t>
+  </si>
+  <si>
+    <t>#   along the member is not one shape, so the row is refused.</t>
+  </si>
+  <si>
     <t># 3.  MODULE  ·  where each member sits inside one module</t>
   </si>
   <si>
@@ -295,9 +373,6 @@
     <t># MODULE</t>
   </si>
   <si>
-    <t>member</t>
-  </si>
-  <si>
     <t>Ref.Pt</t>
   </si>
   <si>
@@ -448,10 +523,49 @@
     <t>FROM</t>
   </si>
   <si>
+    <t>[AZ]</t>
+  </si>
+  <si>
+    <t>[EL]</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
     <t>[title]</t>
   </si>
   <si>
-    <t>#   FROM = FRONT / BACK / LEFT / RIGHT / TOP / BOTTOM</t>
+    <t>#   FROM = FRONT / BACK / LEFT / RIGHT / TOP / BOTTOM / ISO / ISO-NE / ISO-NW /</t>
+  </si>
+  <si>
+    <t>#          ISO-SE / ISO-SW, or 3D with AZ and EL. AZ / EL are for 3D only -</t>
+  </si>
+  <si>
+    <t>#          leave them blank otherwise. The columns never move.</t>
+  </si>
+  <si>
+    <t># PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>SECT</t>
+  </si>
+  <si>
+    <t>#   The other kind of drawing: a part on its own at its standard section, with</t>
+  </si>
+  <si>
+    <t>#   how many were placed - not a thing in place seen from somewhere. PART draws</t>
+  </si>
+  <si>
+    <t>#   the plates, SECT the sections, each with its own scale. A name works in</t>
+  </si>
+  <si>
+    <t>#   place of ALL. Independent of VIEW: either, both or neither.</t>
   </si>
   <si>
     <t>END</t>
@@ -1030,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R154"/>
+  <dimension ref="A1:R182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1476,731 +1590,1019 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="4" t="s">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" t="s">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s">
+        <v>80</v>
+      </c>
+      <c r="I54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="4" t="s">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B63" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I63" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="4" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D64" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B72" s="3" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="4" t="s">
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B74" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="C74" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H72" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K72" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="L72" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="M72" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="O72" s="4" t="s">
+      <c r="I74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="P72" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
+      <c r="J74" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
+      <c r="K74" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="s">
+      <c r="L74" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B75" s="3"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B76" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M76" t="s">
+        <v>103</v>
+      </c>
+      <c r="N76" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B77" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="L79" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="M79" s="4" t="s">
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B80" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="N79" s="4" t="s">
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="O79" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q79" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R79" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="2" t="s">
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B84" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E84" s="4" t="s">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F84" s="4" t="s">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" s="2" t="s">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B91" s="3" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D91" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="J91" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="K91" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="L91" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="M91" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O91" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J91" s="4" t="s">
+      <c r="P91" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B98" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="O98" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="K91" s="4" t="s">
+      <c r="P98" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C92" s="4" t="s">
+      <c r="Q98" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="R98" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B103" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D103" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B110" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I111" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C93" s="4" t="s">
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C94" s="4" t="s">
+      <c r="D112" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B113" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C113" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B103" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B104" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B108" s="5" t="s">
+      <c r="D113" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B113" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B114" s="6"/>
-      <c r="E114" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B115" s="6"/>
-      <c r="E115" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H115" s="7" t="s">
+      <c r="E113" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K113" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B116" s="6"/>
-      <c r="E116" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B117" s="6"/>
-      <c r="E117" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" s="6"/>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B119" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B120" s="6"/>
-      <c r="E120" s="7" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B121" s="6"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="6" t="s">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E122" s="7" t="s">
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="6"/>
-      <c r="E123" s="7" t="s">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B122" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="6"/>
-      <c r="E124" s="7" t="s">
+      <c r="C122" s="4" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="6"/>
-      <c r="E125" s="7" t="s">
+      <c r="D122" s="4" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B126" s="6"/>
-      <c r="E126" s="7" t="s">
+      <c r="E122" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B127" s="6"/>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B128" s="6" t="s">
+      <c r="F122" t="s">
         <v>171</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="G122" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="6"/>
-      <c r="E129" s="7" t="s">
+      <c r="H122" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="6"/>
-      <c r="E130" s="7" t="s">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B123" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="6"/>
-      <c r="E131" s="7" t="s">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B124" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="6"/>
-      <c r="E132" s="7" t="s">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B125" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B133" s="6"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="6" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>177</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="C129" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="6"/>
-      <c r="E135" s="7" t="s">
+      <c r="D129" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B136" s="6"/>
-      <c r="E136" s="7" t="s">
+      <c r="E129" t="s">
+        <v>172</v>
+      </c>
+      <c r="F129" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>177</v>
+      </c>
+      <c r="C130" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B137" s="6"/>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B138" s="6" t="s">
+      <c r="D130" t="s">
+        <v>179</v>
+      </c>
+      <c r="E130" t="s">
+        <v>172</v>
+      </c>
+      <c r="F130" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
         <v>181</v>
       </c>
-      <c r="E138" s="7" t="s">
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="6"/>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="6" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
         <v>183</v>
       </c>
-      <c r="E140" s="7" t="s">
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B141" s="6"/>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="6"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B141" s="6" t="s">
+        <v>187</v>
+      </c>
       <c r="E141" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B142" s="6"/>
       <c r="E142" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B143" s="6"/>
       <c r="E143" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B144" s="6"/>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B145" s="6" t="s">
-        <v>188</v>
-      </c>
+      <c r="E144" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B145" s="6"/>
       <c r="E145" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B146" s="6"/>
-      <c r="E146" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="6"/>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="6" t="s">
-        <v>191</v>
-      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="6"/>
       <c r="E148" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B149" s="6"/>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B151" s="6"/>
       <c r="E151" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B152" s="6"/>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B153" s="6" t="s">
-        <v>196</v>
-      </c>
+      <c r="E152" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B153" s="6"/>
       <c r="E153" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B154" s="6"/>
       <c r="E154" s="7" t="s">
-        <v>198</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="6"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B156" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B157" s="6"/>
+      <c r="E157" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B158" s="6"/>
+      <c r="E158" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B159" s="6"/>
+      <c r="E159" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B160" s="6"/>
+      <c r="E160" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="6"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B162" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B163" s="6"/>
+      <c r="E163" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B164" s="6"/>
+      <c r="E164" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="6"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B166" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="6"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B168" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B169" s="6"/>
+      <c r="E169" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="6"/>
+      <c r="E170" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B171" s="6"/>
+      <c r="E171" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="6"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B173" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B174" s="6"/>
+      <c r="E174" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="6"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B176" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="6"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B178" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B179" s="6"/>
+      <c r="E179" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="6"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B181" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B182" s="6"/>
+      <c r="E182" s="7" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>